--- a/data/volunteers_sworn_in.xlsx
+++ b/data/volunteers_sworn_in.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://georgiacasa-my.sharepoint.com/personal/snpethkar_gacasa_org/Documents/Desktop/inquiry/casa_dashboard_v2/casa_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09A555E0-4135-47C7-8A42-55E304F6A5D1}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC3F2C1-F271-445B-A951-065DE32ECDBA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Counties</t>
   </si>
@@ -207,6 +207,18 @@
   </si>
   <si>
     <t>Southwest Georgia</t>
+  </si>
+  <si>
+    <t>FY 2024 - 4th Qtr</t>
+  </si>
+  <si>
+    <t>FY 2024 - 3rd Qtr</t>
+  </si>
+  <si>
+    <t>FY 2024 - 2nd Qtr</t>
+  </si>
+  <si>
+    <t>FY 2024 - 1st Qtr</t>
   </si>
 </sst>
 </file>
@@ -578,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -587,9 +599,13 @@
     <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -617,8 +633,20 @@
       <c r="I1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -646,8 +674,20 @@
       <c r="I2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -675,8 +715,20 @@
       <c r="I3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -704,8 +756,20 @@
       <c r="I4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -733,8 +797,20 @@
       <c r="I5">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -762,8 +838,20 @@
       <c r="I6">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -791,8 +879,20 @@
       <c r="I7">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>23</v>
+      </c>
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>34</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -820,8 +920,20 @@
       <c r="I8">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -849,8 +961,20 @@
       <c r="I9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>11</v>
+      </c>
+      <c r="K9">
+        <v>21</v>
+      </c>
+      <c r="L9">
+        <v>14</v>
+      </c>
+      <c r="M9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -878,8 +1002,20 @@
       <c r="I10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>21</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -907,8 +1043,20 @@
       <c r="I11">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -936,8 +1084,20 @@
       <c r="I12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -965,8 +1125,20 @@
       <c r="I13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>22</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>9</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -994,8 +1166,20 @@
       <c r="I14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>11</v>
+      </c>
+      <c r="L14">
+        <v>12</v>
+      </c>
+      <c r="M14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1023,8 +1207,20 @@
       <c r="I15">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>4</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1052,8 +1248,20 @@
       <c r="I16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1081,8 +1289,20 @@
       <c r="I17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1110,8 +1330,20 @@
       <c r="I18">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>9</v>
+      </c>
+      <c r="L18">
+        <v>11</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1139,8 +1371,20 @@
       <c r="I19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>6</v>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <v>6</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1168,8 +1412,20 @@
       <c r="I20">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>5</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>6</v>
+      </c>
+      <c r="M20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1197,8 +1453,20 @@
       <c r="I21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1226,8 +1494,20 @@
       <c r="I22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>6</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1255,8 +1535,20 @@
       <c r="I23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>4</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -1284,8 +1576,20 @@
       <c r="I24">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>6</v>
+      </c>
+      <c r="L24">
+        <v>6</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -1313,8 +1617,20 @@
       <c r="I25">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>4</v>
+      </c>
+      <c r="L25">
+        <v>3</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -1342,8 +1658,20 @@
       <c r="I26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>7</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -1371,8 +1699,20 @@
       <c r="I27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>8</v>
+      </c>
+      <c r="L27">
+        <v>6</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -1400,8 +1740,14 @@
       <c r="I28">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <v>5</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -1429,8 +1775,20 @@
       <c r="I29">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -1458,8 +1816,20 @@
       <c r="I30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>7</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -1487,8 +1857,17 @@
       <c r="I31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <v>9</v>
+      </c>
+      <c r="K31">
+        <v>10</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1516,8 +1895,20 @@
       <c r="I32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -1545,8 +1936,20 @@
       <c r="I33">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>4</v>
+      </c>
+      <c r="M33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1568,8 +1971,14 @@
       <c r="I34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -1597,8 +2006,20 @@
       <c r="I35">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35">
+        <v>14</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>8</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -1626,8 +2047,20 @@
       <c r="I36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36">
+        <v>4</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <v>5</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -1655,8 +2088,20 @@
       <c r="I37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -1684,8 +2129,20 @@
       <c r="I38">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38">
+        <v>6</v>
+      </c>
+      <c r="M38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -1713,8 +2170,20 @@
       <c r="I39">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>7</v>
+      </c>
+      <c r="L39">
+        <v>4</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -1742,8 +2211,20 @@
       <c r="I40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J40">
+        <v>4</v>
+      </c>
+      <c r="K40">
+        <v>2</v>
+      </c>
+      <c r="L40">
+        <v>5</v>
+      </c>
+      <c r="M40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -1771,8 +2252,20 @@
       <c r="I41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>3</v>
+      </c>
+      <c r="M41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -1800,8 +2293,20 @@
       <c r="I42">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J42">
+        <v>9</v>
+      </c>
+      <c r="K42">
+        <v>11</v>
+      </c>
+      <c r="L42">
+        <v>8</v>
+      </c>
+      <c r="M42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -1829,8 +2334,20 @@
       <c r="I43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -1858,8 +2375,20 @@
       <c r="I44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1887,8 +2416,20 @@
       <c r="I45">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J45">
+        <v>11</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>3</v>
+      </c>
+      <c r="M45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1916,8 +2457,20 @@
       <c r="I46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>6</v>
+      </c>
+      <c r="L46">
+        <v>5</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1945,8 +2498,20 @@
       <c r="I47">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>6</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -1974,47 +2539,75 @@
       <c r="I48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="B49">
-        <f>SUM(B2:B48)</f>
+        <f t="shared" ref="B49:M49" si="0">SUM(B2:B48)</f>
         <v>159</v>
       </c>
       <c r="C49">
-        <f>SUM(C2:C48)</f>
+        <f t="shared" si="0"/>
         <v>174</v>
       </c>
       <c r="D49">
-        <f>SUM(D2:D48)</f>
+        <f t="shared" si="0"/>
         <v>141</v>
       </c>
       <c r="E49">
-        <f>SUM(E2:E48)</f>
+        <f t="shared" si="0"/>
         <v>181</v>
       </c>
       <c r="F49">
-        <f>SUM(F2:F48)</f>
+        <f t="shared" si="0"/>
         <v>173</v>
       </c>
       <c r="G49">
-        <f>SUM(G2:G48)</f>
+        <f t="shared" si="0"/>
         <v>179</v>
       </c>
       <c r="H49">
-        <f>SUM(H2:H48)</f>
+        <f t="shared" si="0"/>
         <v>133</v>
       </c>
       <c r="I49">
-        <f>SUM(I2:I48)</f>
+        <f t="shared" si="0"/>
         <v>183</v>
       </c>
+      <c r="J49">
+        <f t="shared" si="0"/>
+        <v>199</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="0"/>
+        <v>205</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J2:K48">
-    <sortCondition ref="K48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N3:O45">
+    <sortCondition ref="N2:N45"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
